--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -77,18 +77,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -456,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -494,7 +497,7 @@
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -517,7 +520,7 @@
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -540,7 +543,7 @@
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -563,7 +566,7 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -586,7 +589,7 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -609,7 +612,7 @@
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -632,7 +635,7 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -655,7 +658,7 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -678,7 +681,7 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -701,7 +704,7 @@
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -724,7 +727,7 @@
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -747,7 +750,7 @@
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -770,7 +773,7 @@
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -793,7 +796,7 @@
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -816,7 +819,7 @@
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -839,7 +842,7 @@
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -862,7 +865,7 @@
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -885,7 +888,7 @@
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -908,7 +911,7 @@
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -931,7 +934,7 @@
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -954,7 +957,7 @@
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -977,7 +980,7 @@
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1000,7 +1003,7 @@
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1023,7 +1026,7 @@
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1046,7 +1049,7 @@
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1069,7 +1072,7 @@
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1092,7 +1095,7 @@
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1115,7 +1118,7 @@
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1138,7 +1141,7 @@
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1161,7 +1164,7 @@
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1184,7 +1187,7 @@
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1207,7 +1210,7 @@
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1230,7 +1233,7 @@
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1253,7 +1256,7 @@
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1276,7 +1279,7 @@
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1299,7 +1302,7 @@
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1322,7 +1325,7 @@
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="5" t="n">
         <v>46248</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1344,8 +1347,859 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E38"/>
+  <autoFilter ref="A1:E75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2198,8 +2198,859 @@
         </is>
       </c>
     </row>
+    <row r="76" ht="42" customHeight="1">
+      <c r="A76" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="42" customHeight="1">
+      <c r="A78" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="42" customHeight="1">
+      <c r="A80" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="42" customHeight="1">
+      <c r="A83" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="42" customHeight="1">
+      <c r="A85" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="42" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="42" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="42" customHeight="1">
+      <c r="A90" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="A92" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42" customHeight="1">
+      <c r="A93" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42" customHeight="1">
+      <c r="A94" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42" customHeight="1">
+      <c r="A95" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42" customHeight="1">
+      <c r="A97" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42" customHeight="1">
+      <c r="A98" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42" customHeight="1">
+      <c r="A99" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42" customHeight="1">
+      <c r="A101" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42" customHeight="1">
+      <c r="A103" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42" customHeight="1">
+      <c r="A104" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42" customHeight="1">
+      <c r="A105" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42" customHeight="1">
+      <c r="A106" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42" customHeight="1">
+      <c r="A107" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42" customHeight="1">
+      <c r="A108" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42" customHeight="1">
+      <c r="A109" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42" customHeight="1">
+      <c r="A110" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E75"/>
+  <autoFilter ref="A1:E112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2210,7 +3061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2265,8 +3116,72 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>REMOVIDO</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ADICIONADO</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3049,8 +3049,859 @@
         </is>
       </c>
     </row>
+    <row r="113" ht="42" customHeight="1">
+      <c r="A113" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="42" customHeight="1">
+      <c r="A114" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="42" customHeight="1">
+      <c r="A115" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="42" customHeight="1">
+      <c r="A116" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42" customHeight="1">
+      <c r="A117" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42" customHeight="1">
+      <c r="A118" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42" customHeight="1">
+      <c r="A119" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="42" customHeight="1">
+      <c r="A120" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="42" customHeight="1">
+      <c r="A122" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42" customHeight="1">
+      <c r="A123" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42" customHeight="1">
+      <c r="A124" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42" customHeight="1">
+      <c r="A125" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="42" customHeight="1">
+      <c r="A126" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="A127" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="42" customHeight="1">
+      <c r="A128" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="42" customHeight="1">
+      <c r="A129" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="42" customHeight="1">
+      <c r="A130" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="42" customHeight="1">
+      <c r="A133" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="42" customHeight="1">
+      <c r="A134" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="42" customHeight="1">
+      <c r="A135" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="42" customHeight="1">
+      <c r="A136" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42" customHeight="1">
+      <c r="A137" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="42" customHeight="1">
+      <c r="A138" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="42" customHeight="1">
+      <c r="A141" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="42" customHeight="1">
+      <c r="A142" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="42" customHeight="1">
+      <c r="A143" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="42" customHeight="1">
+      <c r="A144" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="42" customHeight="1">
+      <c r="A145" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="42" customHeight="1">
+      <c r="A147" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="42" customHeight="1">
+      <c r="A148" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="42" customHeight="1">
+      <c r="A149" s="5" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E112"/>
+  <autoFilter ref="A1:E149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/finclass_historico.xlsx
+++ b/finclass_historico.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alterações" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$E$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alterações'!$A$1:$H$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3900,8 +3900,859 @@
         </is>
       </c>
     </row>
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>BR PARTNERS</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>BRBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="42" customHeight="1">
+      <c r="A151" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>GRUPO MATEUS</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>GMAT3</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="42" customHeight="1">
+      <c r="A152" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>KEPLER WEBER</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>KEPL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="42" customHeight="1">
+      <c r="A153" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>PRIO</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>PRIO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="42" customHeight="1">
+      <c r="A154" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>SLC AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>VAMOS</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>VAMO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="42" customHeight="1">
+      <c r="A156" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>A - AÇÕES</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>WIZ CO.</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>WIZC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="42" customHeight="1">
+      <c r="A157" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>BTG CORPORATE OFFICE FUND FII</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>BRCR11</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="42" customHeight="1">
+      <c r="A158" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>CAPITÂNIA SECURITIES II</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>CPTS11</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="42" customHeight="1">
+      <c r="A159" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>PÁTRIA SECURITIES</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>PSEC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>VBI PRIME PROPERTIES</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>PVBI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="42" customHeight="1">
+      <c r="A161" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>RIO BRAVO RENDA VAREJO</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>RBVA11</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>PATRIA PLUS MULTIESTRATÉGIA REAL ESTATE FII</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>RBRX11</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="42" customHeight="1">
+      <c r="A163" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>TRX REAL ESTATE</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>TRXF11</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="42" customHeight="1">
+      <c r="A164" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>VINCI SHOPPING CENTERS FII</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>VISC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="42" customHeight="1">
+      <c r="A165" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>VINCI LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>VILG11</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="42" customHeight="1">
+      <c r="A166" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>XP CRÉDITO IMOBILIÁRIO</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>XPCI11</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="42" customHeight="1">
+      <c r="A167" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>R - REAL ESTATE (FUNDOS IMOBILIÁRIOS)</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>XP MALLS</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>XPML11</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="42" customHeight="1">
+      <c r="A168" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>CDB DO DAYCOVAL, CDB DO BMG OU TESOURO RESERVA</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Pós</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="42" customHeight="1">
+      <c r="A169" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>CPTI11 (CAPITÂNIA INFRA)</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="42" customHeight="1">
+      <c r="A170" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>ETF IRFM11 OU ETF IDKA11</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="42" customHeight="1">
+      <c r="A171" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>JURO11 (SPARTA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>KDIF11 (KINEA INFRA RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="42" customHeight="1">
+      <c r="A173" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>C - CAIXA (RENDA FIXA)</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>TESOURO IPCA 2050</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Renda Fixa Dinâmica</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="42" customHeight="1">
+      <c r="A174" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>ABSOLUTE VERTEX</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>GENOA CAPITAL RADAR</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>IBIUNA HEDGE ST</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42" customHeight="1">
+      <c r="A177" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>KAPITALO KAPPA (OU ZETA)</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>ALUG11 (no exterior é o VNQ)</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="42" customHeight="1">
+      <c r="A179" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>BNDX11 (no exterior é o BNDX)</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="42" customHeight="1">
+      <c r="A180" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>GOLD11 (no exterior é o IAU)</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="42" customHeight="1">
+      <c r="A181" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>MS GLOBAL OPPORTUNITIES DÓLAR</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>Internacional (33.913.562/0001-85)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>USDB11 (no exterior é o BND)</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="42" customHeight="1">
+      <c r="A183" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>WRLD11 (no exterior é o VT)</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="42" customHeight="1">
+      <c r="A184" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="42" customHeight="1">
+      <c r="A185" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>HTEK11</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="42" customHeight="1">
+      <c r="A186" s="5" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>A - ALTERNATIVOS</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>NUCL11</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>Teses alternativas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E149"/>
+  <autoFilter ref="A1:E186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
